--- a/analysis_sample4.xlsx
+++ b/analysis_sample4.xlsx
@@ -6605,7 +6605,7 @@
         <v>245</v>
       </c>
       <c r="R2">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -6661,7 +6661,7 @@
         <v>242</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -6717,7 +6717,7 @@
         <v>170</v>
       </c>
       <c r="R4">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -6773,7 +6773,7 @@
         <v>159</v>
       </c>
       <c r="R5">
-        <v>0.21</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -6829,7 +6829,7 @@
         <v>676</v>
       </c>
       <c r="R6">
-        <v>0.87</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -6885,7 +6885,7 @@
         <v>188</v>
       </c>
       <c r="R7">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -6941,7 +6941,7 @@
         <v>134</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -6997,7 +6997,7 @@
         <v>310</v>
       </c>
       <c r="R9">
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -7165,7 +7165,7 @@
         <v>188</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -7333,7 +7333,7 @@
         <v>18788</v>
       </c>
       <c r="R15">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -7389,7 +7389,7 @@
         <v>337</v>
       </c>
       <c r="R16">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -7445,7 +7445,7 @@
         <v>121</v>
       </c>
       <c r="R17">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -7557,7 +7557,7 @@
         <v>678</v>
       </c>
       <c r="R19">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -7725,7 +7725,7 @@
         <v>223</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -7949,7 +7949,7 @@
         <v>243</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -8005,7 +8005,7 @@
         <v>244</v>
       </c>
       <c r="R27">
-        <v>0.21</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -8061,7 +8061,7 @@
         <v>128</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -8117,7 +8117,7 @@
         <v>102</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -8229,7 +8229,7 @@
         <v>114</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -8285,7 +8285,7 @@
         <v>436</v>
       </c>
       <c r="R32">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -8341,7 +8341,7 @@
         <v>145</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -8397,7 +8397,7 @@
         <v>180</v>
       </c>
       <c r="R34">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -8509,7 +8509,7 @@
         <v>167</v>
       </c>
       <c r="R36">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
@@ -8677,7 +8677,7 @@
         <v>165</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
@@ -8733,7 +8733,7 @@
         <v>144</v>
       </c>
       <c r="R40">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -8845,7 +8845,7 @@
         <v>100</v>
       </c>
       <c r="R42">
-        <v>0.23</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
@@ -8901,7 +8901,7 @@
         <v>300</v>
       </c>
       <c r="R43">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
@@ -8957,7 +8957,7 @@
         <v>248</v>
       </c>
       <c r="R44">
-        <v>0.23</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -9013,7 +9013,7 @@
         <v>379</v>
       </c>
       <c r="R45">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
@@ -9069,7 +9069,7 @@
         <v>163</v>
       </c>
       <c r="R46">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">

--- a/analysis_sample4.xlsx
+++ b/analysis_sample4.xlsx
@@ -6091,7 +6091,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -6103,8 +6103,11 @@
       <b/>
       <color rgb="FFFFFFFF"/>
     </font>
+    <font>
+      <b/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6114,6 +6117,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6B6B"/>
       </patternFill>
     </fill>
     <fill>
@@ -6139,11 +6147,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6556,7 +6566,7 @@
       <c r="A2" t="s">
         <v>18</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>5</v>
       </c>
       <c r="C2" t="s">
@@ -6601,7 +6611,7 @@
       <c r="P2">
         <v>1.2</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="2">
         <v>245</v>
       </c>
       <c r="R2">
@@ -6657,7 +6667,7 @@
       <c r="P3">
         <v>1.8</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="2">
         <v>242</v>
       </c>
       <c r="R3">
@@ -6683,7 +6693,7 @@
       <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
         <v>42</v>
       </c>
       <c r="H4" t="s">
@@ -6724,7 +6734,7 @@
       <c r="A5" t="s">
         <v>48</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>6</v>
       </c>
       <c r="C5" t="s">
@@ -6739,7 +6749,7 @@
       <c r="F5" t="s">
         <v>21</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="2" t="s">
         <v>52</v>
       </c>
       <c r="H5" t="s">
@@ -6748,10 +6758,10 @@
       <c r="I5" t="s">
         <v>54</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="2">
         <v>0.41</v>
       </c>
       <c r="L5" t="s">
@@ -6772,7 +6782,7 @@
       <c r="Q5">
         <v>159</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="3">
         <v>0.57</v>
       </c>
     </row>
@@ -6780,7 +6790,7 @@
       <c r="A6" t="s">
         <v>58</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>1</v>
       </c>
       <c r="C6" t="s">
@@ -6795,7 +6805,7 @@
       <c r="F6" t="s">
         <v>21</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="2" t="s">
         <v>60</v>
       </c>
       <c r="H6" t="s">
@@ -6810,7 +6820,7 @@
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="2" t="s">
         <v>64</v>
       </c>
       <c r="M6" t="s">
@@ -6825,10 +6835,10 @@
       <c r="P6">
         <v>1</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="2">
         <v>676</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="3">
         <v>0.71</v>
       </c>
     </row>
@@ -6863,10 +6873,10 @@
       <c r="J7" t="s">
         <v>72</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="2">
         <v>0.35</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="2" t="s">
         <v>73</v>
       </c>
       <c r="M7" t="s">
@@ -6919,7 +6929,7 @@
       <c r="J8" t="s">
         <v>81</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="2">
         <v>0.39</v>
       </c>
       <c r="L8" t="s">
@@ -6948,7 +6958,7 @@
       <c r="A9" t="s">
         <v>84</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>3</v>
       </c>
       <c r="C9" t="s">
@@ -6963,7 +6973,7 @@
       <c r="F9" t="s">
         <v>21</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="2" t="s">
         <v>86</v>
       </c>
       <c r="H9" t="s">
@@ -6972,13 +6982,13 @@
       <c r="I9" t="s">
         <v>88</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="2" t="s">
         <v>89</v>
       </c>
       <c r="K9">
         <v>0.4</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="2" t="s">
         <v>90</v>
       </c>
       <c r="M9" t="s">
@@ -6993,10 +7003,10 @@
       <c r="P9">
         <v>2</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="2">
         <v>310</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="3">
         <v>0.84</v>
       </c>
     </row>
@@ -7143,7 +7153,7 @@
       <c r="J12" t="s">
         <v>116</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="2">
         <v>0.45</v>
       </c>
       <c r="L12" t="s">
@@ -7299,7 +7309,7 @@
       <c r="F15" t="s">
         <v>21</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="2" t="s">
         <v>139</v>
       </c>
       <c r="H15" t="s">
@@ -7308,13 +7318,13 @@
       <c r="I15" t="s">
         <v>141</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="2" t="s">
         <v>142</v>
       </c>
       <c r="K15">
         <v>0.24</v>
       </c>
-      <c r="L15" t="s">
+      <c r="L15" s="2" t="s">
         <v>143</v>
       </c>
       <c r="M15" t="s">
@@ -7329,10 +7339,10 @@
       <c r="P15">
         <v>6</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="2">
         <v>18788</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="3">
         <v>0.73</v>
       </c>
     </row>
@@ -7385,7 +7395,7 @@
       <c r="P16">
         <v>11</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="2">
         <v>337</v>
       </c>
       <c r="R16">
@@ -7411,7 +7421,7 @@
       <c r="F17" t="s">
         <v>21</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="2" t="s">
         <v>158</v>
       </c>
       <c r="H17" t="s">
@@ -7420,13 +7430,13 @@
       <c r="I17" t="s">
         <v>160</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="2" t="s">
         <v>161</v>
       </c>
       <c r="K17">
         <v>0.21</v>
       </c>
-      <c r="L17" t="s">
+      <c r="L17" s="2" t="s">
         <v>162</v>
       </c>
       <c r="M17" t="s">
@@ -7444,7 +7454,7 @@
       <c r="Q17">
         <v>121</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="3">
         <v>0.53</v>
       </c>
     </row>
@@ -7535,7 +7545,7 @@
       <c r="J19" t="s">
         <v>180</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="2">
         <v>0.57</v>
       </c>
       <c r="L19" t="s">
@@ -7553,7 +7563,7 @@
       <c r="P19">
         <v>4</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="2">
         <v>678</v>
       </c>
       <c r="R19">
@@ -7721,7 +7731,7 @@
       <c r="P22">
         <v>1.6</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="2">
         <v>223</v>
       </c>
       <c r="R22">
@@ -7945,7 +7955,7 @@
       <c r="P26">
         <v>1.8</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" s="2">
         <v>243</v>
       </c>
       <c r="R26">
@@ -7956,7 +7966,7 @@
       <c r="A27" t="s">
         <v>243</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="2">
         <v>6</v>
       </c>
       <c r="C27" t="s">
@@ -7983,7 +7993,7 @@
       <c r="J27" t="s">
         <v>248</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="2">
         <v>0.37</v>
       </c>
       <c r="L27" t="s">
@@ -8001,7 +8011,7 @@
       <c r="P27">
         <v>1.4</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" s="2">
         <v>244</v>
       </c>
       <c r="R27">
@@ -8027,7 +8037,7 @@
       <c r="F28" t="s">
         <v>21</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" s="2" t="s">
         <v>253</v>
       </c>
       <c r="H28" t="s">
@@ -8036,7 +8046,7 @@
       <c r="I28" t="s">
         <v>255</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" s="2" t="s">
         <v>256</v>
       </c>
       <c r="K28">
@@ -8083,7 +8093,7 @@
       <c r="F29" t="s">
         <v>21</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="2" t="s">
         <v>260</v>
       </c>
       <c r="H29" t="s">
@@ -8195,7 +8205,7 @@
       <c r="F31" t="s">
         <v>175</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" s="2" t="s">
         <v>275</v>
       </c>
       <c r="H31" t="s">
@@ -8204,7 +8214,7 @@
       <c r="I31" t="s">
         <v>277</v>
       </c>
-      <c r="J31" t="s">
+      <c r="J31" s="2" t="s">
         <v>278</v>
       </c>
       <c r="K31">
@@ -8281,7 +8291,7 @@
       <c r="P32">
         <v>3.2</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" s="2">
         <v>436</v>
       </c>
       <c r="R32">
@@ -8319,7 +8329,7 @@
       <c r="J33" t="s">
         <v>297</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="2">
         <v>0.32</v>
       </c>
       <c r="L33" t="s">
@@ -8348,7 +8358,7 @@
       <c r="A34" t="s">
         <v>300</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="2">
         <v>4</v>
       </c>
       <c r="C34" t="s">
@@ -8487,10 +8497,10 @@
       <c r="J36" t="s">
         <v>321</v>
       </c>
-      <c r="K36">
+      <c r="K36" s="2">
         <v>0.35</v>
       </c>
-      <c r="L36" t="s">
+      <c r="L36" s="2" t="s">
         <v>322</v>
       </c>
       <c r="M36" t="s">
@@ -8655,7 +8665,7 @@
       <c r="J39" t="s">
         <v>347</v>
       </c>
-      <c r="K39">
+      <c r="K39" s="2">
         <v>0.33</v>
       </c>
       <c r="L39" t="s">
@@ -8711,10 +8721,10 @@
       <c r="J40" t="s">
         <v>353</v>
       </c>
-      <c r="K40">
+      <c r="K40" s="2">
         <v>0.41</v>
       </c>
-      <c r="L40" t="s">
+      <c r="L40" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M40" t="s">
@@ -8811,7 +8821,7 @@
       <c r="F42" t="s">
         <v>21</v>
       </c>
-      <c r="G42" t="s">
+      <c r="G42" s="2" t="s">
         <v>366</v>
       </c>
       <c r="H42" t="s">
@@ -8820,13 +8830,13 @@
       <c r="I42" t="s">
         <v>368</v>
       </c>
-      <c r="J42" t="s">
+      <c r="J42" s="2" t="s">
         <v>369</v>
       </c>
       <c r="K42">
         <v>0.29</v>
       </c>
-      <c r="L42" t="s">
+      <c r="L42" s="2" t="s">
         <v>370</v>
       </c>
       <c r="M42" t="s">
@@ -8897,7 +8907,7 @@
       <c r="P43">
         <v>3.8</v>
       </c>
-      <c r="Q43">
+      <c r="Q43" s="2">
         <v>300</v>
       </c>
       <c r="R43">
@@ -8932,13 +8942,13 @@
       <c r="I44" t="s">
         <v>384</v>
       </c>
-      <c r="J44" t="s">
+      <c r="J44" s="2" t="s">
         <v>385</v>
       </c>
       <c r="K44">
         <v>0.28</v>
       </c>
-      <c r="L44" t="s">
+      <c r="L44" s="2" t="s">
         <v>386</v>
       </c>
       <c r="M44" t="s">
@@ -8953,7 +8963,7 @@
       <c r="P44">
         <v>2.3</v>
       </c>
-      <c r="Q44">
+      <c r="Q44" s="2">
         <v>248</v>
       </c>
       <c r="R44">
@@ -9009,7 +9019,7 @@
       <c r="P45">
         <v>1.7</v>
       </c>
-      <c r="Q45">
+      <c r="Q45" s="2">
         <v>379</v>
       </c>
       <c r="R45">
@@ -9020,7 +9030,7 @@
       <c r="A46" t="s">
         <v>396</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="2">
         <v>4</v>
       </c>
       <c r="C46" t="s">
@@ -9035,7 +9045,7 @@
       <c r="F46" t="s">
         <v>21</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G46" s="2" t="s">
         <v>397</v>
       </c>
       <c r="H46" t="s">
@@ -9050,7 +9060,7 @@
       <c r="K46">
         <v>0.35</v>
       </c>
-      <c r="L46" t="s">
+      <c r="L46" s="2" t="s">
         <v>401</v>
       </c>
       <c r="M46" t="s">
@@ -9148,26 +9158,26 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>415</v>
       </c>
     </row>
@@ -15496,65 +15506,65 @@
     <col min="17" max="20" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="5" t="s">
         <v>415</v>
       </c>
     </row>

--- a/analysis_sample4.xlsx
+++ b/analysis_sample4.xlsx
@@ -63,7 +63,7 @@
     <t>Avg Commits</t>
   </si>
   <si>
-    <t>Avg Changes/h</t>
+    <t>Avg Changes/h over session</t>
   </si>
   <si>
     <t>Index</t>
